--- a/artfynd/A 46080-2025 artfynd.xlsx
+++ b/artfynd/A 46080-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112538849</v>
+        <v>112538848</v>
       </c>
       <c r="B2" t="n">
-        <v>90922</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601078</v>
+        <v>601081</v>
       </c>
       <c r="R2" t="n">
-        <v>6959287</v>
+        <v>6959302</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,12 +775,7 @@
         <v>112538853</v>
       </c>
       <c r="B3" t="n">
-        <v>79676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,7 +807,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601141</v>
+        <v>601142</v>
       </c>
       <c r="R3" t="n">
         <v>6959195</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112538852</v>
+        <v>112538851</v>
       </c>
       <c r="B4" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601095</v>
+        <v>601093</v>
       </c>
       <c r="R4" t="n">
-        <v>6959269</v>
+        <v>6959266</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112538855</v>
+        <v>112538849</v>
       </c>
       <c r="B5" t="n">
-        <v>77499</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601141</v>
+        <v>601078</v>
       </c>
       <c r="R5" t="n">
-        <v>6959195</v>
+        <v>6959287</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112538856</v>
+        <v>112538850</v>
       </c>
       <c r="B6" t="n">
-        <v>78338</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601141</v>
+        <v>601093</v>
       </c>
       <c r="R6" t="n">
-        <v>6959195</v>
+        <v>6959266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112538850</v>
+        <v>112538852</v>
       </c>
       <c r="B7" t="n">
-        <v>90926</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601093</v>
+        <v>601096</v>
       </c>
       <c r="R7" t="n">
-        <v>6959265</v>
+        <v>6959268</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112538848</v>
+        <v>112538854</v>
       </c>
       <c r="B8" t="n">
-        <v>77417</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601081</v>
+        <v>601142</v>
       </c>
       <c r="R8" t="n">
-        <v>6959302</v>
+        <v>6959195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112538851</v>
+        <v>112538856</v>
       </c>
       <c r="B9" t="n">
-        <v>88745</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601093</v>
+        <v>601142</v>
       </c>
       <c r="R9" t="n">
-        <v>6959265</v>
+        <v>6959195</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112538854</v>
+        <v>112538855</v>
       </c>
       <c r="B10" t="n">
-        <v>77498</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,7 +1486,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601141</v>
+        <v>601142</v>
       </c>
       <c r="R10" t="n">
         <v>6959195</v>

--- a/artfynd/A 46080-2025 artfynd.xlsx
+++ b/artfynd/A 46080-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538848</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538853</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538851</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538849</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538850</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538852</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538854</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538856</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,8 +1590,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538855</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>